--- a/SHET/ZPO001/zpo1.xlsx
+++ b/SHET/ZPO001/zpo1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D16DD1-28CD-4494-BCDB-671B923E701A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C8C5C2-F723-4845-868A-23B96B1A75E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>tсраб, с</t>
   </si>
@@ -50,15 +50,6 @@
     <t>Проверка времени срабатывания первой ступени</t>
   </si>
   <si>
-    <t>Входное воздействие</t>
-  </si>
-  <si>
-    <t>Точка</t>
-  </si>
-  <si>
-    <t>Выходное воздействие</t>
-  </si>
-  <si>
     <t>IABC</t>
   </si>
   <si>
@@ -84,6 +75,15 @@
   </si>
   <si>
     <t>tсраб.уст, с</t>
+  </si>
+  <si>
+    <t>Точка входа</t>
+  </si>
+  <si>
+    <t>Точка выхода</t>
+  </si>
+  <si>
+    <t>—</t>
   </si>
 </sst>
 </file>
@@ -471,12 +471,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="49.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="26.140625" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
     <col min="6" max="6" width="26.140625" customWidth="1"/>
@@ -485,107 +485,112 @@
     <col min="9" max="25" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="G2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
+  <mergeCells count="10">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="G3:G6"/>
+    <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/SHET/ZPO001/zpo1.xlsx
+++ b/SHET/ZPO001/zpo1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C8C5C2-F723-4845-868A-23B96B1A75E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3773AD-1E6D-499D-AF93-336757963C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,13 +77,13 @@
     <t>tсраб.уст, с</t>
   </si>
   <si>
-    <t>Точка входа</t>
-  </si>
-  <si>
-    <t>Точка выхода</t>
-  </si>
-  <si>
     <t>—</t>
+  </si>
+  <si>
+    <t>Выход для контроля</t>
+  </si>
+  <si>
+    <t>Вход для проверки</t>
   </si>
 </sst>
 </file>
@@ -487,7 +487,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>11</v>
@@ -527,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -542,7 +542,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -557,7 +557,7 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -566,7 +566,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>

--- a/SHET/ZPO001/zpo1.xlsx
+++ b/SHET/ZPO001/zpo1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3773AD-1E6D-499D-AF93-336757963C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F504FCC-B366-41C5-AE9E-A0767E51FDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>Сигнал</t>
   </si>
   <si>
-    <t>Срабатывание выходного реле при введенном SA1</t>
-  </si>
-  <si>
     <t>Ср. сигн. конт. ДТм АТ 1 цепь</t>
   </si>
   <si>
@@ -84,6 +81,9 @@
   </si>
   <si>
     <t>Вход для проверки</t>
+  </si>
+  <si>
+    <t>Срабатывание выходного реле</t>
   </si>
 </sst>
 </file>
@@ -487,16 +487,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>0</v>
@@ -527,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -536,13 +536,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -551,13 +551,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -566,10 +566,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
